--- a/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
@@ -335,6 +335,62 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$H$2:$H$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$30</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -423,7 +479,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -917,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -959,6 +1015,16 @@
           <t>Bioenergy</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; other</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -982,6 +1048,12 @@
       <c r="G2" t="n">
         <v>0.15262</v>
       </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1005,6 +1077,12 @@
       <c r="G3" t="n">
         <v>0.15262</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1028,6 +1106,12 @@
       <c r="G4" t="n">
         <v>0.15262</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1051,6 +1135,12 @@
       <c r="G5" t="n">
         <v>0.15262</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1074,6 +1164,12 @@
       <c r="G6" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1097,6 +1193,12 @@
       <c r="G7" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1120,6 +1222,12 @@
       <c r="G8" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1143,6 +1251,12 @@
       <c r="G9" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1166,6 +1280,12 @@
       <c r="G10" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1189,6 +1309,12 @@
       <c r="G11" t="n">
         <v>0.16362</v>
       </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1212,6 +1338,12 @@
       <c r="G12" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1235,6 +1367,12 @@
       <c r="G13" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1258,6 +1396,12 @@
       <c r="G14" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1281,6 +1425,12 @@
       <c r="G15" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1304,6 +1454,12 @@
       <c r="G16" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1327,6 +1483,12 @@
       <c r="G17" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1350,6 +1512,12 @@
       <c r="G18" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1373,6 +1541,12 @@
       <c r="G19" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1396,6 +1570,12 @@
       <c r="G20" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1419,6 +1599,12 @@
       <c r="G21" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1442,6 +1628,12 @@
       <c r="G22" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1465,6 +1657,12 @@
       <c r="G23" t="n">
         <v>0.16642</v>
       </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1488,6 +1686,12 @@
       <c r="G24" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1511,6 +1715,12 @@
       <c r="G25" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1534,6 +1744,12 @@
       <c r="G26" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1557,6 +1773,12 @@
       <c r="G27" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1580,6 +1802,12 @@
       <c r="G28" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1603,6 +1831,12 @@
       <c r="G29" t="n">
         <v>0.16717</v>
       </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1625,6 +1859,12 @@
       </c>
       <c r="G30" t="n">
         <v>0.16717</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2782,16 +3022,16 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>45383</v>
+        <v>44531</v>
       </c>
       <c r="B2" t="n">
-        <v>5199.79599</v>
+        <v>5106.85</v>
       </c>
       <c r="C2" t="n">
-        <v>71.13</v>
+        <v>21.15</v>
       </c>
       <c r="D2" t="n">
-        <v>29.05757999999998</v>
+        <v>27.65</v>
       </c>
       <c r="E2" t="n">
         <v>144.3</v>
@@ -2800,125 +3040,125 @@
         <v>8.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2103.655621000001</v>
+        <v>2020.67</v>
       </c>
       <c r="H2" t="n">
-        <v>944.8449999999996</v>
+        <v>943.85</v>
       </c>
       <c r="I2" t="n">
-        <v>461.6250000000001</v>
+        <v>461.63</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/07/BNEE_abril_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/01/Estadistica2021.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>45413</v>
+        <v>44896</v>
       </c>
       <c r="B3" t="n">
-        <v>5215.16599</v>
+        <v>5191.3</v>
       </c>
       <c r="C3" t="n">
-        <v>71.13</v>
+        <v>53.15</v>
       </c>
       <c r="D3" t="n">
-        <v>29.13</v>
+        <v>28.65</v>
       </c>
       <c r="E3" t="n">
-        <v>155.3</v>
+        <v>144.3</v>
       </c>
       <c r="F3" t="n">
         <v>8.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2104.047621</v>
+        <v>2033.18</v>
       </c>
       <c r="H3" t="n">
-        <v>944.745</v>
+        <v>943.85</v>
       </c>
       <c r="I3" t="n">
-        <v>461.625</v>
+        <v>461.63</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/08/BNEE_mayo_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/01/EstadisticaAnual2022-baja-1.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45444</v>
+        <v>45261</v>
       </c>
       <c r="B4" t="n">
-        <v>5215.16599</v>
+        <v>5192.3</v>
       </c>
       <c r="C4" t="n">
         <v>71.13</v>
       </c>
       <c r="D4" t="n">
-        <v>29.12758</v>
+        <v>29.06</v>
       </c>
       <c r="E4" t="n">
-        <v>155.3</v>
+        <v>144.3</v>
       </c>
       <c r="F4" t="n">
         <v>8.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2105.231621</v>
+        <v>2048</v>
       </c>
       <c r="H4" t="n">
-        <v>944.745</v>
+        <v>944.85</v>
       </c>
       <c r="I4" t="n">
-        <v>461.625</v>
+        <v>461.63</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/11/BNEE_junio_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/07/Estadistica-Anual-y-Multianual-del-Sector-Electrico-Ecuatoriano-2023.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45474</v>
+        <v>45383</v>
       </c>
       <c r="B5" t="n">
-        <v>5215.16599</v>
+        <v>5199.79599</v>
       </c>
       <c r="C5" t="n">
         <v>71.13</v>
       </c>
       <c r="D5" t="n">
-        <v>28.12757999999999</v>
+        <v>29.05757999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>155.3</v>
+        <v>144.3</v>
       </c>
       <c r="F5" t="n">
         <v>8.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2119.421621000001</v>
+        <v>2103.655621000001</v>
       </c>
       <c r="H5" t="n">
-        <v>905.3449999999998</v>
+        <v>944.8449999999996</v>
       </c>
       <c r="I5" t="n">
-        <v>488.525</v>
+        <v>461.6250000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/11/BNEE_julio_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/07/BNEE_abril_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45505</v>
+        <v>45413</v>
       </c>
       <c r="B6" t="n">
         <v>5215.16599</v>
@@ -2927,7 +3167,7 @@
         <v>71.13</v>
       </c>
       <c r="D6" t="n">
-        <v>28.12757999999999</v>
+        <v>29.13</v>
       </c>
       <c r="E6" t="n">
         <v>155.3</v>
@@ -2936,32 +3176,32 @@
         <v>8.32</v>
       </c>
       <c r="G6" t="n">
-        <v>2119.421621000001</v>
+        <v>2104.047621</v>
       </c>
       <c r="H6" t="n">
-        <v>905.3449999999998</v>
+        <v>944.745</v>
       </c>
       <c r="I6" t="n">
-        <v>488.525</v>
+        <v>461.625</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/12/BNEE_agosto_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/08/BNEE_mayo_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45536</v>
+        <v>45444</v>
       </c>
       <c r="B7" t="n">
-        <v>5215.165989999999</v>
+        <v>5215.16599</v>
       </c>
       <c r="C7" t="n">
         <v>71.13</v>
       </c>
       <c r="D7" t="n">
-        <v>29.13</v>
+        <v>29.12758</v>
       </c>
       <c r="E7" t="n">
         <v>155.3</v>
@@ -2970,32 +3210,32 @@
         <v>8.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2225.365621</v>
+        <v>2105.231621</v>
       </c>
       <c r="H7" t="n">
-        <v>905.3449999999998</v>
+        <v>944.745</v>
       </c>
       <c r="I7" t="n">
-        <v>488.525</v>
+        <v>461.625</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/12/BNEE_septiembre_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/11/BNEE_junio_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45566</v>
+        <v>45474</v>
       </c>
       <c r="B8" t="n">
-        <v>5215.165989999999</v>
+        <v>5215.16599</v>
       </c>
       <c r="C8" t="n">
         <v>71.13</v>
       </c>
       <c r="D8" t="n">
-        <v>29.13</v>
+        <v>28.12757999999999</v>
       </c>
       <c r="E8" t="n">
         <v>155.3</v>
@@ -3004,7 +3244,7 @@
         <v>8.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2225.365621</v>
+        <v>2119.421621000001</v>
       </c>
       <c r="H8" t="n">
         <v>905.3449999999998</v>
@@ -3014,124 +3254,124 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/03/BNEE_octubre_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/11/BNEE_julio_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45597</v>
+        <v>45505</v>
       </c>
       <c r="B9" t="n">
-        <v>5215.17</v>
+        <v>5215.16599</v>
       </c>
       <c r="C9" t="n">
         <v>71.13</v>
       </c>
       <c r="D9" t="n">
-        <v>29.13</v>
+        <v>28.12757999999999</v>
       </c>
       <c r="E9" t="n">
         <v>155.3</v>
       </c>
       <c r="F9" t="n">
-        <v>11.12</v>
+        <v>8.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2176.98</v>
+        <v>2119.421621000001</v>
       </c>
       <c r="H9" t="n">
-        <v>905.35</v>
+        <v>905.3449999999998</v>
       </c>
       <c r="I9" t="n">
-        <v>488.53</v>
+        <v>488.525</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/04/BNEE_noviembre_2024.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/12/BNEE_agosto_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45627</v>
+        <v>45536</v>
       </c>
       <c r="B10" t="n">
-        <v>5419.16599</v>
+        <v>5215.165989999999</v>
       </c>
       <c r="C10" t="n">
         <v>71.13</v>
       </c>
       <c r="D10" t="n">
-        <v>29.12758</v>
+        <v>29.13</v>
       </c>
       <c r="E10" t="n">
         <v>155.3</v>
       </c>
       <c r="F10" t="n">
-        <v>11.12</v>
+        <v>8.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2163.603621</v>
+        <v>2225.365621</v>
       </c>
       <c r="H10" t="n">
-        <v>943.845</v>
+        <v>905.3449999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>461.625</v>
+        <v>488.525</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/04/BNEE_diciembre_2024_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/12/BNEE_septiembre_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45658</v>
+        <v>45566</v>
       </c>
       <c r="B11" t="n">
-        <v>5416.57</v>
+        <v>5215.165989999999</v>
       </c>
       <c r="C11" t="n">
         <v>71.13</v>
       </c>
       <c r="D11" t="n">
-        <v>29.12758000000001</v>
+        <v>29.13</v>
       </c>
       <c r="E11" t="n">
         <v>155.3</v>
       </c>
       <c r="F11" t="n">
-        <v>11.12</v>
+        <v>8.32</v>
       </c>
       <c r="G11" t="n">
-        <v>2177.71</v>
+        <v>2225.365621</v>
       </c>
       <c r="H11" t="n">
-        <v>905.345</v>
+        <v>905.3449999999998</v>
       </c>
       <c r="I11" t="n">
         <v>488.525</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/05/BNEE_enero_2025_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/03/BNEE_octubre_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="B12" t="n">
-        <v>5416.57</v>
+        <v>5215.17</v>
       </c>
       <c r="C12" t="n">
         <v>71.13</v>
       </c>
       <c r="D12" t="n">
-        <v>29.12758000000001</v>
+        <v>29.13</v>
       </c>
       <c r="E12" t="n">
         <v>155.3</v>
@@ -3140,32 +3380,32 @@
         <v>11.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2177.71</v>
+        <v>2176.98</v>
       </c>
       <c r="H12" t="n">
-        <v>905.345</v>
+        <v>905.35</v>
       </c>
       <c r="I12" t="n">
-        <v>488.525</v>
+        <v>488.53</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/06/BNEE_febrero_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/04/BNEE_noviembre_2024.xls</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45717</v>
+        <v>45627</v>
       </c>
       <c r="B13" t="n">
-        <v>5416.57</v>
+        <v>5419.16599</v>
       </c>
       <c r="C13" t="n">
         <v>71.13</v>
       </c>
       <c r="D13" t="n">
-        <v>29.12758000000001</v>
+        <v>29.12758</v>
       </c>
       <c r="E13" t="n">
         <v>155.3</v>
@@ -3174,23 +3414,23 @@
         <v>11.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2277.603621</v>
+        <v>2163.603621</v>
       </c>
       <c r="H13" t="n">
-        <v>905.345</v>
+        <v>943.845</v>
       </c>
       <c r="I13" t="n">
-        <v>488.525</v>
+        <v>461.625</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/06/BNEE_marzo_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/04/BNEE_diciembre_2024_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>45748</v>
+        <v>45658</v>
       </c>
       <c r="B14" t="n">
         <v>5416.57</v>
@@ -3208,7 +3448,7 @@
         <v>11.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2278.953621</v>
+        <v>2177.71</v>
       </c>
       <c r="H14" t="n">
         <v>905.345</v>
@@ -3218,13 +3458,13 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/07/BNEE_abril_2025_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/05/BNEE_enero_2025_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45809</v>
+        <v>45689</v>
       </c>
       <c r="B15" t="n">
         <v>5416.57</v>
@@ -3242,7 +3482,7 @@
         <v>11.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2380.303621</v>
+        <v>2177.71</v>
       </c>
       <c r="H15" t="n">
         <v>905.345</v>
@@ -3252,16 +3492,16 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/10/BNEE_junio_2025_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/06/BNEE_febrero_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45839</v>
+        <v>45717</v>
       </c>
       <c r="B16" t="n">
-        <v>5417.675989999999</v>
+        <v>5416.57</v>
       </c>
       <c r="C16" t="n">
         <v>71.13</v>
@@ -3276,7 +3516,7 @@
         <v>11.12</v>
       </c>
       <c r="G16" t="n">
-        <v>2382.118621000001</v>
+        <v>2277.603621</v>
       </c>
       <c r="H16" t="n">
         <v>905.345</v>
@@ -3286,16 +3526,16 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/11/BNEE_julio_2025_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/06/BNEE_marzo_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45870</v>
+        <v>45748</v>
       </c>
       <c r="B17" t="n">
-        <v>5417.675989999999</v>
+        <v>5416.57</v>
       </c>
       <c r="C17" t="n">
         <v>71.13</v>
@@ -3310,32 +3550,32 @@
         <v>11.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2382.118621000001</v>
+        <v>2278.953621</v>
       </c>
       <c r="H17" t="n">
-        <v>919.015</v>
+        <v>905.345</v>
       </c>
       <c r="I17" t="n">
         <v>488.525</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/12/BNEE_agosto_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/07/BNEE_abril_2025_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45901</v>
+        <v>45809</v>
       </c>
       <c r="B18" t="n">
-        <v>5417.67599</v>
+        <v>5416.57</v>
       </c>
       <c r="C18" t="n">
         <v>71.13</v>
       </c>
       <c r="D18" t="n">
-        <v>29.13</v>
+        <v>29.12758000000001</v>
       </c>
       <c r="E18" t="n">
         <v>155.3</v>
@@ -3344,32 +3584,32 @@
         <v>11.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2282.118621</v>
+        <v>2380.303621</v>
       </c>
       <c r="H18" t="n">
-        <v>919.0149999999999</v>
+        <v>905.345</v>
       </c>
       <c r="I18" t="n">
         <v>488.525</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/12/BNEE_septiembre_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/10/BNEE_junio_2025_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45931</v>
+        <v>45839</v>
       </c>
       <c r="B19" t="n">
-        <v>5417.67599</v>
+        <v>5417.675989999999</v>
       </c>
       <c r="C19" t="n">
         <v>71.13</v>
       </c>
       <c r="D19" t="n">
-        <v>29.13</v>
+        <v>29.12758000000001</v>
       </c>
       <c r="E19" t="n">
         <v>155.3</v>
@@ -3378,32 +3618,32 @@
         <v>11.12</v>
       </c>
       <c r="G19" t="n">
-        <v>2399.156620999998</v>
+        <v>2382.118621000001</v>
       </c>
       <c r="H19" t="n">
-        <v>919.0149999999999</v>
+        <v>905.345</v>
       </c>
       <c r="I19" t="n">
         <v>488.525</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/01/BNEE_octubre_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/11/BNEE_julio_2025_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="B20" t="n">
-        <v>5417.67599</v>
+        <v>5417.675989999999</v>
       </c>
       <c r="C20" t="n">
         <v>71.13</v>
       </c>
       <c r="D20" t="n">
-        <v>29.13</v>
+        <v>29.12758000000001</v>
       </c>
       <c r="E20" t="n">
         <v>155.3</v>
@@ -3412,125 +3652,125 @@
         <v>11.12</v>
       </c>
       <c r="G20" t="n">
-        <v>2391.473620999998</v>
+        <v>2382.118621000001</v>
       </c>
       <c r="H20" t="n">
-        <v>919.0149999999999</v>
+        <v>919.015</v>
       </c>
       <c r="I20" t="n">
         <v>488.525</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/01/BNEE_noviembre_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/12/BNEE_agosto_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45992</v>
+        <v>45901</v>
       </c>
       <c r="B21" t="n">
-        <v>5388.85301</v>
+        <v>5417.67599</v>
       </c>
       <c r="C21" t="n">
-        <v>71.15001999999998</v>
+        <v>71.13</v>
       </c>
       <c r="D21" t="n">
-        <v>29.12758</v>
+        <v>29.13</v>
       </c>
       <c r="E21" t="n">
-        <v>156.05</v>
+        <v>155.3</v>
       </c>
       <c r="F21" t="n">
         <v>11.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2377.090021</v>
+        <v>2282.118621</v>
       </c>
       <c r="H21" t="n">
-        <v>955.3099999999999</v>
+        <v>919.0149999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>460.125</v>
+        <v>488.525</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/03/BNEE_diciembre_2025.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/12/BNEE_septiembre_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="B22" t="n">
-        <v>5388.85301</v>
+        <v>5417.67599</v>
       </c>
       <c r="C22" t="n">
-        <v>71.15001999999998</v>
+        <v>71.13</v>
       </c>
       <c r="D22" t="n">
-        <v>29.12758</v>
+        <v>29.13</v>
       </c>
       <c r="E22" t="n">
-        <v>156.05</v>
+        <v>155.3</v>
       </c>
       <c r="F22" t="n">
         <v>11.12</v>
       </c>
       <c r="G22" t="n">
-        <v>2434.316770999998</v>
+        <v>2399.156620999998</v>
       </c>
       <c r="H22" t="n">
-        <v>916.8099999999999</v>
+        <v>919.0149999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>487.025</v>
+        <v>488.525</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/04/BNEE_enero_2026_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/01/BNEE_octubre_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46054</v>
+        <v>45962</v>
       </c>
       <c r="B23" t="n">
-        <v>5388.85301</v>
+        <v>5417.67599</v>
       </c>
       <c r="C23" t="n">
-        <v>71.15001999999998</v>
+        <v>71.13</v>
       </c>
       <c r="D23" t="n">
-        <v>29.12758</v>
+        <v>29.13</v>
       </c>
       <c r="E23" t="n">
-        <v>156.05</v>
+        <v>155.3</v>
       </c>
       <c r="F23" t="n">
         <v>11.12</v>
       </c>
       <c r="G23" t="n">
-        <v>2435.366770999999</v>
+        <v>2391.473620999998</v>
       </c>
       <c r="H23" t="n">
-        <v>916.8099999999999</v>
+        <v>919.0149999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>487.025</v>
+        <v>488.525</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/04/BNEE_febrero_2026.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/01/BNEE_noviembre_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46082</v>
+        <v>45992</v>
       </c>
       <c r="B24" t="n">
         <v>5388.85301</v>
@@ -3548,23 +3788,23 @@
         <v>11.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2435.366770999999</v>
+        <v>2377.090021</v>
       </c>
       <c r="H24" t="n">
-        <v>916.8099999999999</v>
+        <v>955.3099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>487.025</v>
+        <v>460.125</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/05/BNEE_marzo_2026.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/03/BNEE_diciembre_2025.xls</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="B25" t="n">
         <v>5388.85301</v>
@@ -3582,29 +3822,29 @@
         <v>11.12</v>
       </c>
       <c r="G25" t="n">
-        <v>2371.792020999998</v>
+        <v>2434.316770999998</v>
       </c>
       <c r="H25" t="n">
-        <v>1033.51375</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>448.125</v>
+        <v>487.025</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/07/BNEE_abril_2026.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/04/BNEE_enero_2026_revACH.xls</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46143</v>
+        <v>46054</v>
       </c>
       <c r="B26" t="n">
-        <v>5384.073009999998</v>
+        <v>5388.85301</v>
       </c>
       <c r="C26" t="n">
-        <v>71.15002000000001</v>
+        <v>71.15001999999998</v>
       </c>
       <c r="D26" t="n">
         <v>29.12758</v>
@@ -3616,29 +3856,29 @@
         <v>11.12</v>
       </c>
       <c r="G26" t="n">
-        <v>2366.865020999998</v>
+        <v>2435.366770999999</v>
       </c>
       <c r="H26" t="n">
-        <v>1033.51375</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>448.125</v>
+        <v>487.025</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/07/BNEE_mayo_2026.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/04/BNEE_febrero_2026.xls</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="B27" t="n">
-        <v>5384.073009999998</v>
+        <v>5388.85301</v>
       </c>
       <c r="C27" t="n">
-        <v>71.15002000000001</v>
+        <v>71.15001999999998</v>
       </c>
       <c r="D27" t="n">
         <v>29.12758</v>
@@ -3650,119 +3890,119 @@
         <v>11.12</v>
       </c>
       <c r="G27" t="n">
-        <v>2367.721020999998</v>
+        <v>2435.366770999999</v>
       </c>
       <c r="H27" t="n">
-        <v>1033.51375</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>448.125</v>
+        <v>487.025</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/09/BNEE_junio_2026_revACH.xls</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/05/BNEE_marzo_2026.xls</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>44531</v>
+        <v>46113</v>
       </c>
       <c r="B28" t="n">
-        <v>5106.85</v>
+        <v>5388.85301</v>
       </c>
       <c r="C28" t="n">
-        <v>21.15</v>
+        <v>71.15001999999998</v>
       </c>
       <c r="D28" t="n">
-        <v>27.65</v>
+        <v>29.12758</v>
       </c>
       <c r="E28" t="n">
-        <v>144.3</v>
+        <v>156.05</v>
       </c>
       <c r="F28" t="n">
-        <v>8.32</v>
+        <v>11.12</v>
       </c>
       <c r="G28" t="n">
-        <v>2020.67</v>
+        <v>2371.792020999998</v>
       </c>
       <c r="H28" t="n">
-        <v>943.85</v>
+        <v>1033.51375</v>
       </c>
       <c r="I28" t="n">
-        <v>461.63</v>
+        <v>448.125</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/01/Estadistica2021.pdf</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/07/BNEE_abril_2026.xls</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>44896</v>
+        <v>46143</v>
       </c>
       <c r="B29" t="n">
-        <v>5191.3</v>
+        <v>5384.073009999998</v>
       </c>
       <c r="C29" t="n">
-        <v>53.15</v>
+        <v>71.15002000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>28.65</v>
+        <v>29.12758</v>
       </c>
       <c r="E29" t="n">
-        <v>144.3</v>
+        <v>156.05</v>
       </c>
       <c r="F29" t="n">
-        <v>8.32</v>
+        <v>11.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2033.18</v>
+        <v>2366.865020999998</v>
       </c>
       <c r="H29" t="n">
-        <v>943.85</v>
+        <v>1033.51375</v>
       </c>
       <c r="I29" t="n">
-        <v>461.63</v>
+        <v>448.125</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2025/01/EstadisticaAnual2022-baja-1.pdf</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/07/BNEE_mayo_2026.xls</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>45261</v>
+        <v>46174</v>
       </c>
       <c r="B30" t="n">
-        <v>5192.3</v>
+        <v>5384.073009999998</v>
       </c>
       <c r="C30" t="n">
-        <v>71.13</v>
+        <v>71.15002000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>29.06</v>
+        <v>29.12758</v>
       </c>
       <c r="E30" t="n">
-        <v>144.3</v>
+        <v>156.05</v>
       </c>
       <c r="F30" t="n">
-        <v>8.32</v>
+        <v>11.12</v>
       </c>
       <c r="G30" t="n">
-        <v>2048</v>
+        <v>2367.721020999998</v>
       </c>
       <c r="H30" t="n">
-        <v>944.85</v>
+        <v>1033.51375</v>
       </c>
       <c r="I30" t="n">
-        <v>461.63</v>
+        <v>448.125</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2024/07/Estadistica-Anual-y-Multianual-del-Sector-Electrico-Ecuatoriano-2023.pdf</t>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/09/BNEE_junio_2026_revACH.xls</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador installed generation capacity (ARCONEL) (to Jun/26)</a:t>
+              <a:t>Ecuador installed generation capacity (ARCONEL) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$30</f>
+              <f>'Chart'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$30</f>
+              <f>'Chart'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$30</f>
+              <f>'Chart'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$30</f>
+              <f>'Chart'!$E$2:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$30</f>
+              <f>'Chart'!$F$2:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$30</f>
+              <f>'Chart'!$G$2:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$30</f>
+              <f>'Chart'!$H$2:$H$31</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$30</f>
+              <f>'Chart'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$30</f>
+              <f>'Chart'!$I$2:$I$31</f>
             </numRef>
           </val>
         </ser>
@@ -836,7 +836,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-12 to 2026-06 (29 rows). Monthly BNEE workbooks are on arconel.gob.ec from April 2024; earlier months were published on the retired ARCERNNR site (www.controlrecursosyenergia.gob.ec, which no longer serves them). For 2021-2023 the series has one row per year, dated 1 December: the December 'Balance nacional de energia electrica' table reprinted in ARCONEL's 'Estadistica Anual y Multianual del Sector Electrico Ecuatoriano' PDF for that year (https://arconel.gob.ec/publicaciones-estadistica-del-sector-electrico-2/). ARCONEL publishes each month about two to three months later. Months missing inside the range: 2025-05.</t>
+          <t>2021-12 to 2026-07 (30 rows). Monthly BNEE workbooks are on arconel.gob.ec from April 2024; earlier months were published on the retired ARCERNNR site (www.controlrecursosyenergia.gob.ec, which no longer serves them). For 2021-2023 the series has one row per year, dated 1 December: the December 'Balance nacional de energia electrica' table reprinted in ARCONEL's 'Estadistica Anual y Multianual del Sector Electrico Ecuatoriano' PDF for that year (https://arconel.gob.ec/publicaciones-estadistica-del-sector-electrico-2/). ARCONEL publishes each month about two to three months later. Months missing inside the range: 2025-05.</t>
         </is>
       </c>
     </row>
@@ -909,21 +909,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Latest row here (2026-06) vs Ember yearly capacity 2025 (GW; diff = (ours - Ember) / Ember):</t>
+          <t>Latest row here (2026-07) vs Ember yearly capacity 2025 (GW; diff = (ours - Ember) / Ember):</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Hydro: 5.384 GW here vs 5.390 GW Ember -&gt; -0.1%</t>
+          <t xml:space="preserve">  Hydro: 5.374 GW here vs 5.390 GW Ember -&gt; -0.3%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gas: 1.034 GW here vs 0.810 GW Ember -&gt; +27.6%</t>
+          <t xml:space="preserve">  Gas: 0.961 GW here vs 0.810 GW Ember -&gt; +18.6%</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oil: 2.816 GW here vs 3.510 GW Ember -&gt; -19.8%</t>
+          <t xml:space="preserve">  Oil: 2.928 GW here vs 3.510 GW Ember -&gt; -16.6%</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total: 9.501 GW here vs 10.080 GW Ember -&gt; -5.7%</t>
+          <t xml:space="preserve">  Total: 9.530 GW here vs 10.080 GW Ember -&gt; -5.5%</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1864,6 +1864,35 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5.37386</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9607100000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.07115</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.92778</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.16717</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,7 +1908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,6 +2981,41 @@
       </c>
       <c r="K30" t="n">
         <v>9500.879999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5373.86</v>
+      </c>
+      <c r="C31" t="n">
+        <v>960.71</v>
+      </c>
+      <c r="D31" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2927.78</v>
+      </c>
+      <c r="I31" t="n">
+        <v>167.17</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9529.799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +3029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4006,6 +4070,40 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5373.858009999997</v>
+      </c>
+      <c r="C31" t="n">
+        <v>71.15002000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29.12758</v>
+      </c>
+      <c r="E31" t="n">
+        <v>156.05</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2467.652020999997</v>
+      </c>
+      <c r="H31" t="n">
+        <v>960.7097499999996</v>
+      </c>
+      <c r="I31" t="n">
+        <v>460.1250000000001</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://arconel.gob.ec/wp-content/uploads/downloads/2026/10/BNEE_julio_2026.xls</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -825,7 +826,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -840,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -862,7 +861,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -898,7 +896,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1027,7 +1024,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B2" t="n">
@@ -1056,7 +1053,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B3" t="n">
@@ -1085,7 +1082,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B4" t="n">
@@ -1114,7 +1111,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B5" t="n">
@@ -1143,7 +1140,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B6" t="n">
@@ -1172,7 +1169,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B7" t="n">
@@ -1201,7 +1198,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B8" t="n">
@@ -1230,7 +1227,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B9" t="n">
@@ -1259,7 +1256,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B10" t="n">
@@ -1288,7 +1285,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B11" t="n">
@@ -1317,7 +1314,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B12" t="n">
@@ -1346,7 +1343,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B13" t="n">
@@ -1375,7 +1372,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B14" t="n">
@@ -1404,7 +1401,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B15" t="n">
@@ -1433,7 +1430,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B16" t="n">
@@ -1462,7 +1459,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B17" t="n">
@@ -1491,7 +1488,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B18" t="n">
@@ -1520,7 +1517,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B19" t="n">
@@ -1549,7 +1546,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B20" t="n">
@@ -1578,7 +1575,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B21" t="n">
@@ -1607,7 +1604,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B22" t="n">
@@ -1636,7 +1633,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B23" t="n">
@@ -1665,7 +1662,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B24" t="n">
@@ -1694,7 +1691,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B25" t="n">
@@ -1723,7 +1720,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B26" t="n">
@@ -1752,7 +1749,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B27" t="n">
@@ -1781,7 +1778,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B28" t="n">
@@ -1810,7 +1807,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B29" t="n">
@@ -1839,7 +1836,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B30" t="n">
@@ -1868,7 +1865,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B31" t="n">

--- a/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ecuador installed generation capacity (ARCONEL) (to Jul/26)</a:t>
             </a:r>
           </a:p>
@@ -290,7 +291,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -318,7 +319,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -346,7 +347,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -374,7 +375,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>

--- a/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/ecuador_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,6 +841,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -862,6 +863,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -897,6 +899,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1028,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B2" t="n">
@@ -1054,7 +1057,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B3" t="n">
@@ -1083,7 +1086,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B4" t="n">
@@ -1112,7 +1115,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B5" t="n">
@@ -1141,7 +1144,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B6" t="n">
@@ -1170,7 +1173,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B7" t="n">
@@ -1199,7 +1202,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B8" t="n">
@@ -1228,7 +1231,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B9" t="n">
@@ -1257,7 +1260,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B10" t="n">
@@ -1286,7 +1289,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B11" t="n">
@@ -1315,7 +1318,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B12" t="n">
@@ -1344,7 +1347,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B13" t="n">
@@ -1373,7 +1376,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B14" t="n">
@@ -1402,7 +1405,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B15" t="n">
@@ -1431,7 +1434,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B16" t="n">
@@ -1460,7 +1463,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B17" t="n">
@@ -1489,7 +1492,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B18" t="n">
@@ -1518,7 +1521,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B19" t="n">
@@ -1547,7 +1550,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B20" t="n">
@@ -1576,7 +1579,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B21" t="n">
@@ -1605,7 +1608,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B22" t="n">
@@ -1634,7 +1637,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B23" t="n">
@@ -1663,7 +1666,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B24" t="n">
@@ -1692,7 +1695,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B25" t="n">
@@ -1721,7 +1724,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B26" t="n">
@@ -1750,7 +1753,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B27" t="n">
@@ -1779,7 +1782,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B28" t="n">
@@ -1808,7 +1811,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B29" t="n">
@@ -1837,7 +1840,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B30" t="n">
@@ -1866,7 +1869,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B31" t="n">
